--- a/ForHome8/DataScience/model_report_task07.xlsx
+++ b/ForHome8/DataScience/model_report_task07.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="31">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t xml:space="preserve">{'agglomerative__linkage': 'complete', 'agglomerative__distance_threshold': np.float64(1.3689999999999998)}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is the best model, because it has the highest silhouette metric. The similar pages can be seen colored with the same color in the dendrogram.</t>
   </si>
   <si>
     <t xml:space="preserve">dbscan Clustering on ['0', '1', '2', '3', '4', '5', '6', '7', '8', '9', '10', '11', '12', '13', '14', '15', '16', '17', '18', '19', '20', '21', '22', '23', '24', '25', '26', '27', '28', '29', '30', '31', '32', '33', '34', '35', '36', '37', '38', '39', '40', '41', '42', '43', '44', '45', '46', '47', '48', '49', '50', '51', '52', '53', '54', '55', '56', '57', '58', '59', '60', '61', '62', '63', '64', '65', '66', '67', '68', '69', '70', '71', '72', '73', '74', '75', '76', '77', '78', '79', '80', '81', '82', '83', '84', '85', '86', '87', '88', '89', '90', '91', '92', '93', '94', '95', '96', '97', '98', '99', '100', '101', '102', '103', '104', '105', '106', '107', '108', '109', '110', '111', '112', '113', '114', '115', '116', '117', '118', '119', '120', '121', '122', '123', '124', '125', '126', '127', '128', '129', '130', '131', '132', '133', '134', '135', '136', '137', '138', '139', '140', '141', '142', '143', '144', '145', '146', '147', '148', '149', '150', '151', '152', '153', '154', '155', '156', '157', '158', '159', '160', '161', '162', '163', '164', '165', '166', '167', '168', '169', '170', '171', '172', '173', '174', '175', '176', '177', '178', '179', '180', '181', '182', '183', '184', '185', '186', '187', '188', '189', '190', '191', '192', '193', '194', '195', '196', '197', '198', '199', '200', '201', '202', '203', '204', '205', '206', '207', '208', '209', '210', '211', '212', '213', '214', '215', '216', '217', '218', '219', '220', '221', '222', '223', '224', '225', '226', '227', '228', '229', '230', '231', '232', '233', '234', '235', '236', '237', '238', '239', '240', '241', '242', '243', '244', '245', '246', '247', '248', '249', '250', '251', '252', '253', '254', '255', '256', '257', '258', '259', '260', '261', '262', '263', '264', '265', '266', '267', '268', '269', '270', '271', '272', '273', '274', '275', '276', '277', '278', '279', '280', '281', '282', '283', '284', '285', '286', '287', '288', '289', '290', '291', '292', '293', '294', '295', '296', '297', '298', '299', '300', '301', '302', '303', '304', '305', '306', '307', '308', '309', '310', '311', '312', '313', '314', '315', '316', '317', '318', '319', '320', '321', '322', '323', '324', '325', '326', '327', '328', '329', '330', '331', '332', '333', '334', '335', '336', '337', '338', '339', '340', '341', '342', '343', '344', '345', '346', '347', '348', '349', '350', '351', '352', '353', '354', '355', '356', '357', '358', '359', '360', '361', '362', '363', '364', '365', '366', '367', '368', '369', '370', '371', '372', '373', '374', '375', '376', '377', '378', '379', '380', '381', '382', '383', '384', '385', '386', '387', '388', '389', '390', '391', '392', '393', '394', '395', '396', '397', '398', '399', '400', '401', '402', '403', '404', '405', '406', '407', '408', '409', '410', '411', '412', '413', '414', '415', '416', '417', '418', '419', '420', '421', '422', '423', '424', '425', '426', '427', '428', '429', '430', '431', '432', '433', '434', '435', '436', '437', '438', '439', '440', '441', '442', '443', '444', '445', '446', '447', '448', '449', '450', '451', '452', '453', '454', '455', '456', '457', '458', '459', '460', '461', '462', '463', '464', '465', '466', '467', '468', '469', '470', '471', '472', '473', '474', '475', '476', '477', '478', '479', '480', '481', '482', '483', '484', '485', '486', '487', '488', '489', '490', '491', '492', '493', '494', '495', '496', '497', '498', '499', '500', '501', '502', '503', '504', '505', '506', '507', '508', '509', '510', '511', '512', '513', '514', '515', '516', '517', '518', '519', '520', '521', '522', '523', '524', '525', '526', '527', '528', '529', '530', '531', '532', '533', '534', '535', '536', '537', '538', '539', '540', '541', '542', '543', '544', '545', '546', '547', '548', '549', '550', '551', '552', '553', '554', '555', '556', '557', '558', '559', '560', '561', '562', '563', '564', '565', '566', '567', '568', '569', '570', '571', '572', '573', '574', '575', '576', '577', '578', '579', '580', '581', '582', '583', '584', '585', '586', '587', '588', '589', '590', '591', '592', '593', '594', '595', '596', '597', '598', '599', '600', '601', '602', '603', '604', '605', '606', '607', '608', '609', '610', '611', '612', '613', '614', '615', '616', '617', '618', '619', '620', '621', '622', '623', '624', '625', '626', '627', '628', '629', '630', '631', '632', '633', '634', '635', '636', '637', '638', '639', '640', '641', '642', '643', '644', '645', '646', '647', '648', '649', '650', '651', '652', '653', '654', '655', '656', '657', '658', '659', '660', '661', '662', '663', '664', '665', '666', '667', '668', '669', '670', '671', '672', '673', '674', '675', '676', '677', '678', '679', '680', '681', '682', '683', '684', '685', '686', '687', '688', '689', '690', '691', '692', '693', '694', '695', '696', '697', '698', '699', '700', '701', '702', '703', '704', '705', '706', '707', '708', '709', '710', '711', '712', '713', '714', '715', '716', '717', '718', '719', '720', '721', '722', '723', '724', '725', '726', '727', '728', '729', '730', '731', '732', '733', '734', '735', '736', '737', '738', '739', '740', '741', '742', '743', '744', '745', '746', '747', '748', '749', '750', '751', '752', '753', '754', '755', '756', '757', '758', '759', '760', '761', '762', '763', '764', '765', '766', '767', '768', '769', '770', '771', '772', '773', '774', '775', '776', '777', '778', '779', '780', '781', '782', '783', '784', '785', '786', '787', '788', '789', '790', '791', '792', '793', '794', '795', '796', '797', '798', '799', '800', '801', '802', '803', '804', '805', '806', '807', '808', '809', '810', '811', '812', '813', '814', '815', '816', '817', '818', '819', '820', '821', '822', '823', '824', '825', '826', '827', '828', '829', '830', '831', '832', '833', '834', '835', '836', '837', '838', '839', '840', '841', '842', '843', '844', '845', '846', '847', '848', '849', '850', '851', '852', '853', '854', '855', '856', '857', '858', '859', '860', '861', '862', '863', '864', '865', '866', '867', '868', '869', '870', '871', '872', '873', '874', '875', '876', '877', '878', '879', '880', '881', '882', '883', '884', '885', '886', '887', '888', '889', '890', '891', '892', '893', '894', '895', '896', '897', '898', '899', '900', '901', '902', '903', '904', '905', '906', '907', '908', '909', '910', '911', '912', '913', '914', '915', '916', '917', '918', '919', '920', '921', '922', '923', '924', '925', '926', '927', '928', '929', '930', '931', '932', '933', '934', '935', '936', '937', '938', '939', '940', '941', '942', '943', '944', '945', '946', '947', '948', '949', '950', '951', '952', '953', '954', '955', '956', '957', '958', '959', '960', '961', '962', '963', '964', '965', '966', '967', '968', '969', '970', '971', '972', '973', '974', '975', '976', '977', '978', '979', '980', '981', '982', '983', '984', '985', '986', '987', '988', '989', '990', '991', '992', '993', '994', '995', '996', '997', '998', '999', '1000', '1001', '1002', '1003', '1004', '1005', '1006', '1007', '1008', '1009', '1010', '1011', '1012', '1013', '1014', '1015', '1016', '1017', '1018', '1019', '1020', '1021', '1022', '1023', '1024', '1025', '1026', '1027', '1028', '1029', '1030', '1031', '1032', '1033', '1034', '1035', '1036', '1037', '1038', '1039', '1040', '1041', '1042', '1043', '1044', '1045', '1046', '1047', '1048', '1049', '1050', '1051', '1052', '1053', '1054', '1055', '1056', '1057', '1058', '1059', '1060', '1061', '1062', '1063', '1064', '1065', '1066', '1067', '1068', '1069', '1070', '1071', '1072', '1073', '1074', '1075', '1076', '1077', '1078', '1079', '1080', '1081', '1082', '1083', '1084', '1085', '1086', '1087', '1088', '1089', '1090', '1091', '1092', '1093', '1094', '1095', '1096', '1097', '1098', '1099', '1100', '1101', '1102', '1103', '1104', '1105', '1106', '1107', '1108', '1109', '1110', '1111', '1112', '1113', '1114', '1115', '1116', '1117', '1118', '1119', '1120', '1121', '1122', '1123', '1124', '1125', '1126', '1127', '1128', '1129', '1130', '1131', '1132', '1133', '1134', '1135', '1136', '1137', '1138', '1139', '1140', '1141', '1142', '1143', '1144', '1145', '1146', '1147', '1148', '1149', '1150', '1151', '1152', '1153', '1154', '1155', '1156', '1157', '1158', '1159', '1160', '1161', '1162', '1163', '1164', '1165', '1166', '1167', '1168', '1169', '1170', '1171', '1172', '1173', '1174', '1175', '1176', '1177', '1178', '1179', '1180', '1181', '1182', '1183', '1184', '1185', '1186', '1187', '1188', '1189', '1190', '1191', '1192', '1193', '1194', '1195', '1196', '1197', '1198', '1199', '1200', '1201', '1202', '1203', '1204', '1205', '1206', '1207', '1208', '1209', '1210', '1211', '1212', '1213', '1214', '1215', '1216', '1217', '1218', '1219', '1220', '1221', '1222', '1223', '1224', '1225', '1226', '1227', '1228', '1229', '1230', '1231', '1232', '1233', '1234', '1235', '1236', '1237', '1238', '1239', '1240', '1241', '1242', '1243', '1244', '1245', '1246', '1247', '1248', '1249', '1250', '1251', '1252', '1253', '1254', '1255', '1256', '1257', '1258', '1259', '1260', '1261', '1262', '1263', '1264', '1265', '1266', '1267', '1268', '1269', '1270', '1271', '1272', '1273', '1274', '1275', '1276', '1277', '1278', '1279', '1280', '1281', '1282', '1283', '1284', '1285', '1286', '1287', '1288', '1289', '1290', '1291', '1292', '1293', '1294', '1295', '1296', '1297', '1298', '1299', '1300', '1301', '1302', '1303', '1304', '1305', '1306', '1307', '1308', '1309', '1310', '1311', '1312', '1313', '1314', '1315', '1316', '1317', '1318', '1319', '1320', '1321', '1322', '1323', '1324', '1325', '1326', '1327', '1328', '1329', '1330', '1331', '1332', '1333', '1334', '1335', '1336', '1337', '1338', '1339', '1340', '1341', '1342', '1343', '1344', '1345', '1346', '1347', '1348', '1349', '1350', '1351', '1352', '1353', '1354', '1355', '1356', '1357', '1358', '1359', '1360', '1361', '1362', '1363', '1364', '1365', '1366', '1367', '1368', '1369', '1370', '1371', '1372', '1373', '1374', '1375', '1376', '1377', '1378', '1379', '1380', '1381', '1382', '1383', '1384', '1385', '1386', '1387', '1388', '1389', '1390', '1391', '1392', '1393', '1394', '1395', '1396', '1397', '1398', '1399', '1400', '1401', '1402', '1403', '1404', '1405', '1406', '1407', '1408', '1409', '1410', '1411', '1412', '1413', '1414', '1415', '1416', '1417', '1418', '1419', '1420', '1421', '1422', '1423', '1424', '1425', '1426', '1427', '1428', '1429', '1430', '1431', '1432', '1433', '1434', '1435', '1436', '1437', '1438', '1439', '1440', '1441', '1442', '1443', '1444', '1445', '1446', '1447', '1448', '1449', '1450', '1451', '1452', '1453', '1454', '1455', '1456', '1457', '1458', '1459', '1460', '1461', '1462', '1463', '1464', '1465', '1466', '1467', '1468', '1469', '1470', '1471', '1472', '1473', '1474', '1475', '1476', '1477', '1478', '1479', '1480', '1481', '1482', '1483', '1484', '1485', '1486', '1487', '1488', '1489', '1490', '1491', '1492', '1493', '1494', '1495', '1496', '1497', '1498', '1499', '1500', '1501', '1502', '1503', '1504', '1505', '1506', '1507', '1508', '1509', '1510', '1511', '1512', '1513', '1514', '1515', '1516', '1517', '1518', '1519', '1520', '1521', '1522', '1523', '1524', '1525', '1526', '1527', '1528', '1529', '1530', '1531', '1532', '1533', '1534', '1535', '1536', '1537', '1538', '1539', '1540', '1541', '1542', '1543', '1544', '1545', '1546', '1547', '1548', '1549', '1550', '1551', '1552', '1553', '1554', '1555', '1556', '1557', '1558', '1559', '1560', '1561', '1562', '1563', '1564', '1565', '1566', '1567', '1568', '1569', '1570', '1571', '1572', '1573', '1574', '1575', '1576', '1577', '1578', '1579', '1580', '1581', '1582', '1583', '1584', '1585', '1586', '1587', '1588', '1589', '1590', '1591', '1592', '1593', '1594', '1595', '1596', '1597', '1598', '1599', '1600', '1601', '1602', '1603', '1604', '1605', '1606', '1607', '1608', '1609', '1610', '1611', '1612', '1613', '1614', '1615', '1616', '1617', '1618', '1619', '1620', '1621', '1622', '1623', '1624', '1625', '1626', '1627', '1628', '1629', '1630', '1631', '1632', '1633', '1634', '1635', '1636', '1637', '1638', '1639', '1640', '1641', '1642', '1643', '1644', '1645', '1646', '1647', '1648', '1649', '1650', '1651', '1652', '1653', '1654', '1655', '1656', '1657', '1658', '1659', '1660', '1661', '1662', '1663', '1664', '1665', '1666', '1667', '1668', '1669', '1670', '1671', '1672', '1673', '1674', '1675', '1676', '1677', '1678', '1679', '1680', '1681', '1682', '1683', '1684', '1685', '1686', '1687', '1688', '1689', '1690', '1691', '1692', '1693', '1694', '1695', '1696', '1697', '1698', '1699', '1700', '1701', '1702', '1703', '1704', '1705', '1706', '1707', '1708', '1709', '1710', '1711', '1712', '1713', '1714', '1715', '1716', '1717', '1718', '1719', '1720', '1721', '1722', '1723', '1724', '1725', '1726', '1727', '1728', '1729', '1730', '1731', '1732', '1733', '1734', '1735', '1736', '1737', '1738', '1739', '1740', '1741', '1742', '1743', '1744', '1745', '1746', '1747', '1748', '1749', '1750', '1751', '1752', '1753', '1754', '1755', '1756', '1757', '1758', '1759', '1760', '1761', '1762', '1763', '1764', '1765', '1766', '1767', '1768', '1769', '1770', '1771', '1772', '1773', '1774', '1775', '1776', '1777', '1778', '1779', '1780', '1781', '1782', '1783', '1784', '1785', '1786', '1787', '1788', '1789', '1790', '1791', '1792', '1793', '1794', '1795', '1796', '1797', '1798', '1799', '1800', '1801', '1802', '1803', '1804', '1805', '1806', '1807', '1808', '1809', '1810', '1811', '1812', '1813', '1814', '1815', '1816', '1817', '1818', '1819', '1820', '1821', '1822', '1823', '1824', '1825', '1826', '1827', '1828', '1829', '1830', '1831', '1832', '1833', '1834', '1835', '1836', '1837', '1838', '1839', '1840', '1841', '1842', '1843', '1844', '1845', '1846', '1847', '1848', '1849', '1850', '1851', '1852', '1853', '1854', '1855', '1856', '1857', '1858', '1859', '1860', '1861', '1862', '1863', '1864', '1865', '1866', '1867', '1868', '1869', '1870', '1871', '1872', '1873', '1874', '1875', '1876', '1877', '1878', '1879', '1880', '1881', '1882', '1883', '1884', '1885', '1886', '1887', '1888', '1889', '1890', '1891', '1892', '1893', '1894', '1895', '1896', '1897', '1898', '1899', '1900', '1901', '1902', '1903', '1904', '1905', '1906', '1907', '1908', '1909', '1910', '1911', '1912', '1913', '1914', '1915', '1916', '1917', '1918', '1919', '1920', '1921', '1922', '1923', '1924', '1925', '1926', '1927', '1928', '1929', '1930', '1931', '1932', '1933', '1934', '1935', '1936', '1937', '1938', '1939', '1940', '1941', '1942', '1943', '1944', '1945', '1946', '1947', '1948', '1949', '1950', '1951', '1952', '1953', '1954', '1955', '1956', '1957', '1958', '1959', '1960', '1961', '1962', '1963', '1964', '1965', '1966', '1967', '1968', '1969', '1970', '1971', '1972', '1973', '1974', '1975', '1976', '1977', '1978', '1979', '1980', '1981', '1982', '1983', '1984', '1985', '1986', '1987', '1988', '1989', '1990', '1991', '1992', '1993', '1994', '1995', '1996', '1997', '1998', '1999', '2000', '2001', '2002', '2003', '2004', '2005', '2006', '2007', '2008', '2009', '2010', '2011', '2012', '2013', '2014', '2015', '2016', '2017', '2018', '2019', '2020', '2021', '2022', '2023', '2024', '2025', '2026', '2027', '2028', '2029', '2030', '2031', '2032', '2033', '2034', '2035', '2036', '2037', '2038', '2039', '2040', '2041', '2042', '2043', '2044', '2045', '2046', '2047', '2048', '2049', '2050', '2051', '2052', '2053', '2054', '2055', '2056', '2057', '2058', '2059', '2060', '2061', '2062', '2063', '2064', '2065', '2066', '2067', '2068', '2069', '2070', '2071', '2072', '2073', '2074', '2075', '2076', '2077', '2078', '2079', '2080', '2081', '2082', '2083', '2084', '2085', '2086', '2087', '2088', '2089', '2090', '2091', '2092', '2093', '2094', '2095', '2096', '2097', '2098', '2099', '2100', '2101', '2102', '2103', '2104', '2105', '2106', '2107', '2108', '2109', '2110', '2111', '2112', '2113', '2114', '2115', '2116', '2117', '2118', '2119', '2120', '2121', '2122', '2123', '2124', '2125', '2126', '2127', '2128', '2129', '2130', '2131', '2132', '2133', '2134', '2135', '2136', '2137', '2138', '2139', '2140', '2141', '2142', '2143', '2144', '2145', '2146', '2147', '2148', '2149', '2150', '2151', '2152', '2153', '2154', '2155', '2156', '2157', '2158', '2159', '2160', '2161', '2162', '2163', '2164', '2165', '2166', '2167', '2168', '2169', '2170', '2171', '2172', '2173', '2174', '2175', '2176', '2177', '2178', '2179', '2180', '2181', '2182', '2183', '2184', '2185', '2186', '2187', '2188', '2189', '2190', '2191', '2192', '2193', '2194', '2195', '2196', '2197', '2198', '2199', '2200', '2201', '2202', '2203', '2204', '2205', '2206', '2207', '2208', '2209', '2210', '2211', '2212', '2213', '2214', '2215', '2216', '2217', '2218', '2219', '2220', '2221', '2222', '2223', '2224', '2225', '2226', '2227', '2228', '2229', '2230', '2231', '2232', '2233', '2234', '2235', '2236', '2237', '2238', '2239', '2240', '2241', '2242', '2243', '2244', '2245', '2246', '2247', '2248', '2249', '2250', '2251', '2252', '2253', '2254', '2255', '2256', '2257', '2258', '2259', '2260', '2261', '2262', '2263', '2264', '2265', '2266', '2267', '2268', '2269', '2270', '2271', '2272', '2273', '2274', '2275', '2276', '2277', '2278', '2279', '2280', '2281', '2282', '2283', '2284', '2285', '2286', '2287', '2288', '2289', '2290', '2291', '2292', '2293', '2294', '2295', '2296', '2297', '2298', '2299', '2300', '2301', '2302', '2303', '2304', '2305', '2306', '2307', '2308', '2309', '2310', '2311', '2312', '2313', '2314', '2315', '2316', '2317', '2318', '2319', '2320', '2321', '2322', '2323', '2324', '2325', '2326', '2327', '2328', '2329', '2330', '2331', '2332', '2333', '2334', '2335', '2336', '2337', '2338', '2339', '2340', '2341', '2342', '2343', '2344', '2345', '2346', '2347', '2348', '2349', '2350', '2351', '2352', '2353', '2354', '2355', '2356', '2357', '2358', '2359', '2360', '2361', '2362', '2363', '2364', '2365', '2366', '2367', '2368', '2369', '2370', '2371', '2372', '2373', '2374', '2375', '2376', '2377', '2378', '2379', '2380', '2381', '2382', '2383', '2384', '2385', '2386', '2387', '2388', '2389', '2390', '2391', '2392', '2393', '2394', '2395', '2396', '2397', '2398', '2399', '2400', '2401', '2402', '2403', '2404', '2405', '2406', '2407', '2408', '2409', '2410', '2411', '2412', '2413', '2414', '2415', '2416', '2417', '2418', '2419', '2420', '2421', '2422', '2423', '2424', '2425', '2426', '2427', '2428', '2429', '2430', '2431', '2432', '2433', '2434', '2435', '2436', '2437', '2438', '2439', '2440', '2441', '2442', '2443', '2444', '2445', '2446', '2447', '2448', '2449', '2450', '2451', '2452', '2453', '2454', '2455', '2456', '2457', '2458', '2459', '2460', '2461', '2462', '2463', '2464', '2465', '2466', '2467', '2468', '2469', '2470', '2471', '2472', '2473', '2474', '2475', '2476', '2477', '2478', '2479', '2480', '2481', '2482', '2483', '2484', '2485', '2486', '2487', '2488', '2489', '2490', '2491', '2492', '2493', '2494', '2495', '2496', '2497', '2498', '2499', '2500', '2501', '2502', '2503', '2504', '2505', '2506', '2507', '2508', '2509', '2510', '2511', '2512', '2513', '2514', '2515', '2516', '2517', '2518', '2519', '2520', '2521', '2522', '2523', '2524', '2525', '2526', '2527', '2528', '2529', '2530', '2531', '2532', '2533', '2534', '2535', '2536', '2537', '2538', '2539', '2540', '2541', '2542', '2543', '2544', '2545', '2546', '2547', '2548', '2549', '2550', '2551', '2552', '2553', '2554', '2555', '2556', '2557', '2558', '2559', '2560', '2561', '2562', '2563', '2564', '2565', '2566', '2567', '2568', '2569', '2570', '2571', '2572', '2573', '2574', '2575', '2576', '2577', '2578', '2579', '2580', '2581', '2582', '2583', '2584', '2585', '2586', '2587', '2588', '2589', '2590', '2591', '2592', '2593', '2594', '2595', '2596', '2597', '2598', '2599', '2600', '2601', '2602', '2603', '2604', '2605', '2606', '2607', '2608', '2609', '2610', '2611', '2612', '2613', '2614', '2615', '2616', '2617', '2618', '2619', '2620', '2621', '2622', '2623', '2624', '2625', '2626', '2627', '2628', '2629', '2630', '2631', '2632', '2633', '2634', '2635', '2636', '2637', '2638', '2639', '2640', '2641', '2642', '2643', '2644', '2645', '2646', '2647', '2648', '2649', '2650', '2651', '2652', '2653', '2654', '2655', '2656', '2657', '2658', '2659', '2660', '2661', '2662', '2663', '2664', '2665', '2666', '2667', '2668', '2669', '2670', '2671', '2672', '2673', '2674', '2675', '2676', '2677', '2678', '2679', '2680', '2681', '2682', '2683', '2684', '2685', '2686', '2687', '2688', '2689', '2690', '2691', '2692', '2693', '2694', '2695', '2696', '2697', '2698', '2699', '2700', '2701', '2702', '2703', '2704', '2705', '2706', '2707', '2708', '2709', '2710', '2711', '2712', '2713', '2714', '2715', '2716', '2717', '2718', '2719', '2720', '2721', '2722', '2723', '2724', '2725', '2726', '2727', '2728', '2729', '2730', '2731', '2732', '2733', '2734', '2735', '2736', '2737', '2738', '2739', '2740', '2741', '2742', '2743', '2744', '2745', '2746', '2747', '2748', '2749', '2750', '2751', '2752', '2753', '2754', '2755', '2756', '2757', '2758', '2759', '2760', '2761', '2762', '2763', '2764', '2765', '2766', '2767', '2768', '2769', '2770', '2771', '2772', '2773', '2774', '2775', '2776', '2777', '2778', '2779', '2780', '2781', '2782', '2783', '2784', '2785', '2786', '2787', '2788', '2789', '2790', '2791', '2792', '2793', '2794', '2795', '2796', '2797', '2798', '2799', '2800', '2801', '2802', '2803', '2804', '2805', '2806', '2807', '2808', '2809', '2810', '2811', '2812', '2813', '2814', '2815', '2816', '2817', '2818', '2819', '2820', '2821', '2822', '2823', '2824', '2825', '2826', '2827', '2828', '2829', '2830', '2831', '2832', '2833', '2834', '2835', '2836', '2837', '2838', '2839', '2840', '2841', '2842', '2843', '2844', '2845', '2846', '2847', '2848', '2849', '2850', '2851', '2852', '2853', '2854', '2855', '2856', '2857', '2858', '2859', '2860', '2861', '2862', '2863', '2864', '2865', '2866', '2867', '2868', '2869', '2870', '2871', '2872', '2873', '2874', '2875', '2876', '2877', '2878', '2879', '2880', '2881', '2882', '2883', '2884', '2885', '2886', '2887', '2888', '2889', '2890', '2891', '2892', '2893', '2894', '2895', '2896', '2897', '2898', '2899', '2900', '2901', '2902', '2903', '2904', '2905', '2906', '2907', '2908', '2909', '2910', '2911', '2912', '2913', '2914', '2915', '2916', '2917', '2918', '2919', '2920', '2921', '2922', '2923', '2924', '2925', '2926', '2927', '2928', '2929', '2930', '2931', '2932', '2933', '2934', '2935', '2936', '2937', '2938', '2939', '2940', '2941', '2942', '2943', '2944', '2945', '2946', '2947', '2948', '2949', '2950', '2951', '2952', '2953', '2954', '2955', '2956', '2957', '2958', '2959', '2960', '2961', '2962', '2963', '2964', '2965', '2966', '2967', '2968', '2969', '2970', '2971', '2972', '2973', '2974', '2975', '2976', '2977', '2978', '2979', '2980', '2981', '2982', '2983', '2984', '2985', '2986', '2987', '2988', '2989', '2990', '2991', '2992', '2993', '2994', '2995', '2996', '2997', '2998', '2999', '3000', '3001', '3002', '3003', '3004', '3005', '3006', '3007', '3008', '3009', '3010', '3011', '3012', '3013', '3014', '3015', '3016', '3017', '3018', '3019', '3020', '3021', '3022', '3023', '3024', '3025', '3026', '3027', '3028', '3029', '3030', '3031', '3032', '3033', '3034', '3035', '3036', '3037', '3038', '3039', '3040', '3041', '3042', '3043', '3044', '3045', '3046', '3047', '3048', '3049', '3050', '3051', '3052', '3053', '3054', '3055', '3056', '3057', '3058', '3059', '3060', '3061', '3062', '3063', '3064', '3065', '3066', '3067', '3068', '3069', '3070', '3071', '3072', '3073', '3074', '3075', '3076', '3077', '3078', '3079', '3080', '3081', '3082', '3083', '3084', '3085', '3086', '3087', '3088', '3089', '3090', '3091', '3092', '3093', '3094', '3095', '3096', '3097', '3098', '3099', '3100', '3101', '3102', '3103', '3104', '3105', '3106', '3107', '3108', '3109', '3110', '3111', '3112', '3113', '3114', '3115', '3116', '3117', '3118', '3119', '3120', '3121', '3122', '3123', '3124', '3125', '3126', '3127', '3128', '3129', '3130', '3131', '3132', '3133', '3134', '3135', '3136', '3137', '3138', '3139', '3140', '3141', '3142', '3143', '3144', '3145', '3146', '3147', '3148', '3149', '3150', '3151', '3152', '3153', '3154', '3155', '3156', '3157', '3158', '3159', '3160', '3161', '3162', '3163', '3164', '3165', '3166', '3167', '3168', '3169', '3170', '3171', '3172', '3173', '3174', '3175', '3176', '3177', '3178', '3179', '3180', '3181', '3182', '3183', '3184', '3185', '3186', '3187', '3188', '3189', '3190', '3191', '3192', '3193', '3194', '3195', '3196', '3197', '3198', '3199', '3200', '3201', '3202', '3203', '3204', '3205', '3206', '3207', '3208', '3209', '3210', '3211', '3212', '3213', '3214', '3215', '3216', '3217', '3218', '3219', '3220', '3221', '3222', '3223', '3224', '3225', '3226', '3227', '3228', '3229', '3230', '3231', '3232', '3233', '3234', '3235', '3236', '3237', '3238', '3239', '3240', '3241', '3242', '3243', '3244', '3245', '3246', '3247', '3248', '3249', '3250', '3251', '3252', '3253', '3254', '3255', '3256', '3257', '3258', '3259', '3260', '3261', '3262', '3263', '3264', '3265', '3266', '3267', '3268', '3269', '3270', '3271', '3272', '3273', '3274', '3275', '3276', '3277', '3278', '3279', '3280', '3281', '3282', '3283', '3284', '3285', '3286', '3287', '3288', '3289', '3290', '3291', '3292', '3293', '3294', '3295', '3296', '3297', '3298', '3299', '3300', '3301', '3302', '3303', '3304', '3305', '3306', '3307', '3308', '3309', '3310', '3311', '3312', '3313', '3314', '3315', '3316', '3317', '3318', '3319', '3320', '3321', '3322', '3323', '3324', '3325', '3326', '3327', '3328', '3329', '3330', '3331', '3332', '3333', '3334', '3335', '3336', '3337', '3338', '3339', '3340', '3341', '3342', '3343', '3344', '3345', '3346', '3347', '3348', '3349', '3350', '3351', '3352', '3353', '3354', '3355', '3356', '3357', '3358', '3359', '3360', '3361', '3362', '3363', '3364', '3365', '3366', '3367', '3368', '3369', '3370', '3371', '3372', '3373', '3374', '3375', '3376', '3377', '3378', '3379', '3380', '3381', '3382', '3383', '3384', '3385', '3386', '3387', '3388', '3389', '3390', '3391', '3392', '3393', '3394', '3395', '3396', '3397', '3398', '3399', '3400', '3401', '3402', '3403', '3404', '3405', '3406', '3407', '3408', '3409', '3410', '3411', '3412', '3413', '3414', '3415', '3416', '3417', '3418', '3419', '3420', '3421', '3422', '3423', '3424', '3425', '3426', '3427', '3428', '3429', '3430', '3431', '3432', '3433', '3434', '3435', '3436', '3437', '3438', '3439', '3440', '3441', '3442', '3443', '3444', '3445', '3446', '3447', '3448', '3449', '3450', '3451', '3452', '3453', '3454', '3455', '3456', '3457', '3458', '3459', '3460', '3461', '3462', '3463', '3464', '3465', '3466', '3467', '3468', '3469', '3470', '3471', '3472', '3473', '3474', '3475', '3476', '3477', '3478', '3479', '3480', '3481', '3482', '3483', '3484', '3485', '3486', '3487', '3488', '3489', '3490', '3491', '3492', '3493', '3494', '3495', '3496', '3497', '3498', '3499', '3500', '3501', '3502', '3503', '3504', '3505', '3506', '3507', '3508', '3509', '3510', '3511', '3512', '3513', '3514', '3515', '3516', '3517', '3518', '3519', '3520', '3521', '3522', '3523', '3524', '3525', '3526', '3527', '3528', '3529', '3530', '3531', '3532', '3533', '3534', '3535', '3536', '3537', '3538', '3539', '3540', '3541', '3542', '3543', '3544', '3545', '3546', '3547', '3548', '3549', '3550', '3551', '3552', '3553', '3554', '3555', '3556', '3557', '3558', '3559', '3560', '3561', '3562', '3563', '3564', '3565', '3566', '3567', '3568', '3569', '3570', '3571', '3572', '3573', '3574', '3575', '3576', '3577', '3578', '3579', '3580', '3581', '3582', '3583', '3584', '3585', '3586', '3587', '3588', '3589', '3590', '3591', '3592', '3593', '3594', '3595', '3596', '3597', '3598', '3599', '3600', '3601', '3602', '3603', '3604', '3605', '3606', '3607', '3608', '3609', '3610', '3611', '3612', '3613', '3614', '3615', '3616', '3617', '3618', '3619', '3620', '3621', '3622', '3623', '3624', '3625', '3626', '3627', '3628', '3629', '3630', '3631', '3632', '3633', '3634', '3635', '3636', '3637', '3638', '3639', '3640', '3641', '3642', '3643', '3644', '3645', '3646', '3647', '3648', '3649', '3650', '3651', '3652', '3653', '3654', '3655', '3656', '3657', '3658', '3659', '3660', '3661', '3662', '3663', '3664', '3665', '3666', '3667', '3668', '3669', '3670', '3671', '3672', '3673', '3674', '3675', '3676', '3677', '3678', '3679', '3680', '3681', '3682', '3683', '3684', '3685', '3686', '3687', '3688', '3689', '3690', '3691', '3692', '3693', '3694', '3695', '3696', '3697', '3698', '3699', '3700', '3701', '3702', '3703', '3704', '3705', '3706', '3707', '3708', '3709', '3710', '3711', '3712', '3713', '3714', '3715', '3716', '3717', '3718', '3719', '3720', '3721', '3722', '3723', '3724', '3725', '3726', '3727', '3728', '3729', '3730', '3731', '3732', '3733', '3734', '3735', '3736', '3737', '3738', '3739', '3740', '3741', '3742', '3743', '3744', '3745', '3746', '3747', '3748', '3749', '3750', '3751', '3752', '3753', '3754', '3755', '3756', '3757', '3758', '3759', '3760', '3761', '3762', '3763', '3764', '3765', '3766', '3767', '3768', '3769', '3770', '3771', '3772', '3773', '3774', '3775', '3776', '3777', '3778', '3779', '3780', '3781', '3782', '3783', '3784', '3785', '3786', '3787', '3788', '3789', '3790', '3791', '3792', '3793', '3794', '3795', '3796', '3797', '3798', '3799', '3800', '3801', '3802', '3803', '3804', '3805', '3806', '3807', '3808', '3809', '3810', '3811', '3812', '3813', '3814', '3815', '3816', '3817', '3818', '3819', '3820', '3821', '3822', '3823', '3824', '3825', '3826', '3827', '3828', '3829', '3830', '3831', '3832', '3833', '3834', '3835', '3836', '3837', '3838', '3839', '3840', '3841', '3842', '3843', '3844', '3845', '3846', '3847', '3848', '3849', '3850', '3851', '3852', '3853', '3854', '3855', '3856', '3857', '3858', '3859', '3860', '3861', '3862', '3863', '3864', '3865', '3866', '3867', '3868', '3869', '3870', '3871', '3872', '3873', '3874', '3875', '3876', '3877', '3878', '3879', '3880', '3881', '3882', '3883', '3884', '3885', '3886', '3887', '3888', '3889', '3890', '3891', '3892', '3893', '3894', '3895', '3896', '3897', '3898', '3899', '3900', '3901', '3902', '3903', '3904', '3905', '3906', '3907', '3908', '3909', '3910', '3911', '3912', '3913', '3914', '3915', '3916', '3917', '3918', '3919', '3920', '3921', '3922', '3923', '3924', '3925', '3926', '3927', '3928', '3929', '3930', '3931', '3932', '3933', '3934', '3935', '3936', '3937', '3938', '3939', '3940', '3941', '3942', '3943', '3944', '3945', '3946', '3947', '3948', '3949', '3950', '3951', '3952', '3953', '3954', '3955', '3956', '3957', '3958', '3959', '3960', '3961', '3962', '3963', '3964', '3965', '3966', '3967', '3968', '3969', '3970', '3971', '3972', '3973', '3974', '3975', '3976', '3977', '3978', '3979', '3980', '3981', '3982', '3983', '3984', '3985', '3986', '3987', '3988', '3989', '3990', '3991', '3992', '3993', '3994', '3995', '3996', '3997', '3998', '3999', '4000', '4001', '4002', '4003', '4004', '4005', '4006', '4007', '4008', '4009', '4010', '4011', '4012', '4013', '4014', '4015', '4016', '4017', '4018', '4019', '4020', '4021', '4022', '4023', '4024', '4025', '4026', '4027', '4028', '4029', '4030', '4031', '4032', '4033', '4034', '4035', '4036', '4037', '4038', '4039', '4040', '4041', '4042', '4043', '4044', '4045', '4046', '4047', '4048', '4049', '4050', '4051', '4052', '4053', '4054', '4055', '4056', '4057', '4058', '4059', '4060', '4061', '4062', '4063', '4064', '4065', '4066', '4067', '4068', '4069', '4070', '4071', '4072', '4073', '4074', '4075', '4076', '4077', '4078', '4079', '4080', '4081', '4082', '4083', '4084', '4085', '4086', '4087', '4088', '4089', '4090', '4091', '4092', '4093', '4094', '4095', '4096', '4097', '4098', '4099', '4100', '4101', '4102', '4103', '4104', '4105', '4106', '4107', '4108', '4109', '4110', '4111', '4112', '4113', '4114', '4115', '4116', '4117', '4118', '4119', '4120', '4121', '4122', '4123', '4124', '4125', '4126', '4127', '4128', '4129', '4130', '4131', '4132', '4133', '4134', '4135', '4136', '4137', '4138', '4139', '4140', '4141', '4142', '4143', '4144', '4145', '4146', '4147', '4148', '4149', '4150', '4151', '4152', '4153', '4154', '4155', '4156', '4157', '4158', '4159', '4160', '4161', '4162', '4163', '4164', '4165', '4166', '4167', '4168', '4169', '4170', '4171', '4172', '4173', '4174', '4175', '4176', '4177', '4178', '4179', '4180', '4181', '4182', '4183', '4184', '4185', '4186', '4187', '4188', '4189', '4190', '4191', '4192', '4193', '4194', '4195', '4196', '4197', '4198', '4199', '4200', '4201', '4202', '4203', '4204', '4205', '4206', '4207', '4208', '4209', '4210', '4211', '4212', '4213', '4214', '4215', '4216', '4217', '4218', '4219', '4220', '4221', '4222', '4223', '4224', '4225', '4226', '4227', '4228', '4229', '4230', '4231',</t>
@@ -144,12 +147,18 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77BC65"/>
+        <bgColor rgb="FF99CC00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -186,9 +195,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -200,6 +221,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF77BC65"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -214,9 +295,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -229,8 +310,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="190440"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="190440"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -251,9 +332,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -266,8 +347,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="6534000"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="6534000"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -288,9 +369,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -303,8 +384,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12565440" y="6534000"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="12571200" y="6534000"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -325,9 +406,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -340,8 +421,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="12877920"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="12877920"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -362,9 +443,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -377,8 +458,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12565440" y="12877920"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="12571200" y="12877920"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -399,9 +480,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -414,8 +495,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="19221480"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="19221480"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -436,9 +517,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -451,8 +532,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12565440" y="19221480"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="12571200" y="19221480"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -473,9 +554,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -488,8 +569,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="25565040"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="25565040"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -510,9 +591,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -525,8 +606,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12565440" y="25565040"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="12571200" y="25565040"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -547,9 +628,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -562,8 +643,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="31908600"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="31908600"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -584,9 +665,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -599,8 +680,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12565440" y="31908600"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="12571200" y="31908600"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -621,9 +702,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -636,8 +717,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="38252520"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="38252520"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -658,9 +739,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -673,8 +754,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12565440" y="38252520"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="12571200" y="38252520"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -695,9 +776,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -710,8 +791,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="44596080"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="44596080"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -732,9 +813,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -747,8 +828,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12565440" y="44596080"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="12571200" y="44596080"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -769,9 +850,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -784,8 +865,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="50939640"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="50939640"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -806,9 +887,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -821,8 +902,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12565440" y="50939640"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="12571200" y="50939640"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -843,9 +924,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -858,8 +939,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="57283200"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="57283200"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -880,9 +961,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -895,8 +976,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12565440" y="57283200"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="12571200" y="57283200"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -917,9 +998,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -932,8 +1013,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="63627120"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="63627120"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -954,9 +1035,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -969,8 +1050,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="69970680"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="69970680"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -991,9 +1072,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1006,8 +1087,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="76314240"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="76314240"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1028,9 +1109,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1043,8 +1124,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="82657800"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="82657800"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1065,9 +1146,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1080,8 +1161,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="89001720"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="89001720"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1102,9 +1183,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1117,8 +1198,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="95345280"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="95345280"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1139,9 +1220,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1154,8 +1235,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="101688840"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="101688840"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1176,9 +1257,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1191,8 +1272,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="108032400"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="108032400"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1213,9 +1294,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1228,8 +1309,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5509440" y="114376320"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="5514840" y="114376320"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1250,7 +1331,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1268,10 +1349,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="100"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="142.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="142.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1493,27 +1574,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" s="2" customFormat="true" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>13125</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>0.137894301721865</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>-113.789430172187</v>
       </c>
-      <c r="I10" s="0" t="n">
-        <v>0</v>
+      <c r="I10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1541,7 +1627,7 @@
     </row>
     <row r="12" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>16</v>
@@ -1550,7 +1636,7 @@
         <v>13125</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" s="0" t="n">
         <v>0.110276705570357</v>
@@ -1564,7 +1650,7 @@
     </row>
     <row r="13" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>16</v>
@@ -1573,7 +1659,7 @@
         <v>13125</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F13" s="0" t="n">
         <v>0.107394837814535</v>
@@ -1587,7 +1673,7 @@
     </row>
     <row r="14" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>16</v>
@@ -1596,7 +1682,7 @@
         <v>13125</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="0" t="n">
         <v>0.0454955063683746</v>
@@ -1610,7 +1696,7 @@
     </row>
     <row r="15" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>16</v>
@@ -1619,7 +1705,7 @@
         <v>13125</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G15" s="0" t="n">
         <v>0</v>
@@ -1630,7 +1716,7 @@
     </row>
     <row r="16" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>16</v>
@@ -1639,7 +1725,7 @@
         <v>13125</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>0.071208678832443</v>
@@ -1653,7 +1739,7 @@
     </row>
     <row r="17" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>16</v>
@@ -1662,7 +1748,7 @@
         <v>13125</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F17" s="0" t="n">
         <v>0.0694414167523309</v>
@@ -1676,7 +1762,7 @@
     </row>
     <row r="18" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>16</v>
@@ -1685,7 +1771,7 @@
         <v>13125</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="0" t="n">
         <v>0.071208678832443</v>
@@ -1699,7 +1785,7 @@
     </row>
     <row r="19" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>16</v>
@@ -1708,7 +1794,7 @@
         <v>13125</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F19" s="0" t="n">
         <v>0.037766718897661</v>
@@ -1722,7 +1808,7 @@
     </row>
     <row r="20" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>16</v>
@@ -1731,7 +1817,7 @@
         <v>13125</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F20" s="0" t="n">
         <v>0.111966804366176</v>
